--- a/Assets/DataTable/Kindergarten_Tycoon.xlsx
+++ b/Assets/DataTable/Kindergarten_Tycoon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Y\Kindergarten_Tycoon\Assets\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B31D8B0-9043-4828-B006-A2E675006DFA}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96A5EC8-8231-4571-A2AD-84457583510E}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="4" xr2:uid="{8967E840-0208-4204-843E-AF892D6CF31B}"/>
+    <workbookView xWindow="31950" yWindow="4485" windowWidth="12255" windowHeight="7560" xr2:uid="{8967E840-0208-4204-843E-AF892D6CF31B}"/>
   </bookViews>
   <sheets>
     <sheet name="FurnitureTable" sheetId="5" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="135">
   <si>
     <t>ZoneType</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -157,66 +157,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>WhiteBoard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ZoneType.MainRoom</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Storage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CDPlayer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HandWasher</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ZoneType.RestRoom</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TowelBox</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Umbrellas</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShoesStorage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Crayons</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Toilet01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Toilet02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bedding01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bedding02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BathRoomStair</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>FurnitureItemId01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -233,46 +181,18 @@
     <t>FurnitureItemId05</t>
   </si>
   <si>
-    <t>TrashBox</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PaintBook</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ZoneType.PlayRoom</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Blocks</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TeddyBear</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Light</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ZoneType.SleepRoom</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Water</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ZoneType.DiningRoom</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Sink</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SetFurnitureCount</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -393,34 +313,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Table01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Table02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Plant01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Plant02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Refrige</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Counter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnterRug</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Sprites/Objects/Room/WallPaper</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -493,14 +385,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Sprites/Objects/furniture/WhiteBoard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprites/Objects/furniture/Storage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Sprites/Objects/furniture/CDPlayer</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -525,10 +409,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Sprites/Objects/furniture/Blocks</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Sprites/Objects/furniture/TeddyBear</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -562,6 +442,142 @@
   </si>
   <si>
     <t>Prefab/Canvas_POPUP/POPUP_HIbiscusPlay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/Objects/furniture/Board</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Sprites/Objects/furniture/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>BookShelf</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/Objects/furniture/ToyBox</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파란 화장실 칸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노란 화장실 칸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>곰돌이 이불</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>꿈꾸는 이불</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>병아리 테이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분홍 테이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>둥근 식물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림 세트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신발장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우산꽂이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보드판</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>책꽂이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CD 장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화장실 세면대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수건 보관함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발 받침대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쓰레기통</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장난감 상자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림책</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>곰돌이 인형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정수기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉장고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카운터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>싱크대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>러그</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZoneType.Entrance</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -569,7 +585,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -592,6 +608,21 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="5">
@@ -634,7 +665,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -656,6 +687,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -671,6 +705,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1067,10 +1105,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1105,10 +1143,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>42</v>
+        <v>108</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1143,10 +1181,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1183,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1223,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -1265,10 +1303,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -1309,10 +1347,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1344,10 +1382,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1379,10 +1417,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1414,10 +1452,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>39</v>
+        <v>116</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1435,7 +1473,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="s">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -1449,10 +1487,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>38</v>
+        <v>117</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1470,7 +1508,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="Q12">
         <v>1</v>
@@ -1484,10 +1522,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1505,27 +1543,27 @@
         <v>2</v>
       </c>
       <c r="P13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>106</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>33</v>
+      <c r="C14" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
@@ -1540,7 +1578,7 @@
         <v>3</v>
       </c>
       <c r="P14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -1554,10 +1592,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1575,7 +1613,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -1589,10 +1627,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>35</v>
+        <v>121</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -1610,7 +1648,7 @@
         <v>4</v>
       </c>
       <c r="P16" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q16">
         <v>2</v>
@@ -1624,16 +1662,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
         <v>900</v>
@@ -1645,7 +1683,7 @@
         <v>2</v>
       </c>
       <c r="P17" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q17">
         <v>2</v>
@@ -1659,10 +1697,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1680,7 +1718,7 @@
         <v>2</v>
       </c>
       <c r="P18" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -1694,10 +1732,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1715,7 +1753,7 @@
         <v>2</v>
       </c>
       <c r="P19" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -1729,10 +1767,10 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1750,7 +1788,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -1764,10 +1802,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1785,7 +1823,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -1799,10 +1837,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>55</v>
+        <v>127</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1820,7 +1858,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -1834,16 +1872,16 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="1">
         <v>700</v>
@@ -1855,7 +1893,7 @@
         <v>2</v>
       </c>
       <c r="P23" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -1869,10 +1907,10 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -1890,7 +1928,7 @@
         <v>2</v>
       </c>
       <c r="P24" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -1904,16 +1942,16 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1">
         <v>1200</v>
@@ -1925,7 +1963,7 @@
         <v>3</v>
       </c>
       <c r="P25" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -1939,10 +1977,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="E26">
         <v>2</v>
@@ -1960,7 +1998,7 @@
         <v>2</v>
       </c>
       <c r="P26" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -1974,10 +2012,10 @@
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>2</v>
@@ -1995,7 +2033,7 @@
         <v>3</v>
       </c>
       <c r="P27" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="Q27">
         <v>4</v>
@@ -2009,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2059,28 +2097,28 @@
         <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E1" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="F1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="H1" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I1" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -2127,16 +2165,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>1</v>
@@ -2145,18 +2183,18 @@
         <v>2</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B2" t="b">
         <v>0</v>
@@ -2174,7 +2212,7 @@
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -2188,7 +2226,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -2203,7 +2241,7 @@
         <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -2211,7 +2249,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" t="b">
         <v>0</v>
@@ -2229,7 +2267,7 @@
         <v>4</v>
       </c>
       <c r="H4" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -2237,13 +2275,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -2258,7 +2296,7 @@
         <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -2269,13 +2307,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B6" t="b">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -2290,7 +2328,7 @@
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -2301,13 +2339,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -2322,7 +2360,7 @@
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -2333,13 +2371,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B8" t="b">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="D8">
         <v>12</v>
@@ -2354,7 +2392,7 @@
         <v>4</v>
       </c>
       <c r="H8" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -2379,31 +2417,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -2598,21 +2636,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C1" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D1" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -2621,12 +2659,12 @@
         <v>300</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B3">
         <v>30</v>
@@ -2635,7 +2673,7 @@
         <v>300</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/DataTable/Kindergarten_Tycoon.xlsx
+++ b/Assets/DataTable/Kindergarten_Tycoon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Y\Kindergarten_Tycoon\Assets\DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7d0e8186344fb24c/yeon_project/Kindergarten_Tycoon/Assets/DataTable/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96A5EC8-8231-4571-A2AD-84457583510E}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{F96A5EC8-8231-4571-A2AD-84457583510E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA3FCC8F-586E-409C-9666-1AF605C160D4}"/>
   <bookViews>
-    <workbookView xWindow="31950" yWindow="4485" windowWidth="12255" windowHeight="7560" xr2:uid="{8967E840-0208-4204-843E-AF892D6CF31B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8967E840-0208-4204-843E-AF892D6CF31B}"/>
   </bookViews>
   <sheets>
     <sheet name="FurnitureTable" sheetId="5" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="130">
   <si>
     <t>ZoneType</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -133,10 +133,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ZoneType.Enterance</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>usingPos01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -175,12 +171,6 @@
     <t>FurnitureItemId03</t>
   </si>
   <si>
-    <t>FurnitureItemId04</t>
-  </si>
-  <si>
-    <t>FurnitureItemId05</t>
-  </si>
-  <si>
     <t>ZoneType.PlayRoom</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -317,10 +307,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Sprites/Objects/Room/EnteranceTile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Sprites/Objects/Room/MainRoomTile</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -430,10 +416,6 @@
   </si>
   <si>
     <t>Sprites/Objects/furniture/Sink</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprites/Objects/furniture/EnterRug</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -573,11 +555,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>러그</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ZoneType.Entrance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/Objects/Room/EntranceTile</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1028,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51A5764C-C03A-CD47-8779-963111FB9250}">
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -1070,13 +1052,13 @@
         <v>10</v>
       </c>
       <c r="I1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>11</v>
@@ -1105,10 +1087,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1143,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1181,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1221,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1261,10 +1243,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -1282,7 +1264,7 @@
         <v>17</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K6" s="6"/>
       <c r="L6" t="s">
@@ -1303,10 +1285,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -1324,10 +1306,10 @@
         <v>17</v>
       </c>
       <c r="J7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="L7" t="s">
         <v>23</v>
@@ -1347,10 +1329,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1382,10 +1364,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1417,10 +1399,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1452,10 +1434,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1473,7 +1455,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -1487,10 +1469,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1508,7 +1490,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="Q12">
         <v>1</v>
@@ -1522,10 +1504,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1543,7 +1525,7 @@
         <v>2</v>
       </c>
       <c r="P13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -1557,10 +1539,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1578,7 +1560,7 @@
         <v>3</v>
       </c>
       <c r="P14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -1592,10 +1574,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1613,7 +1595,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -1627,10 +1609,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -1648,7 +1630,7 @@
         <v>4</v>
       </c>
       <c r="P16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q16">
         <v>2</v>
@@ -1662,10 +1644,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1683,7 +1665,7 @@
         <v>2</v>
       </c>
       <c r="P17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q17">
         <v>2</v>
@@ -1697,10 +1679,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1718,7 +1700,7 @@
         <v>2</v>
       </c>
       <c r="P18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q18">
         <v>2</v>
@@ -1732,10 +1714,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1753,7 +1735,7 @@
         <v>2</v>
       </c>
       <c r="P19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -1767,10 +1749,10 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1788,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="Q20">
         <v>3</v>
@@ -1802,10 +1784,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1823,7 +1805,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -1837,10 +1819,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1858,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="Q22">
         <v>3</v>
@@ -1872,10 +1854,10 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1893,7 +1875,7 @@
         <v>2</v>
       </c>
       <c r="P23" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -1907,10 +1889,10 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -1928,7 +1910,7 @@
         <v>2</v>
       </c>
       <c r="P24" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -1942,10 +1924,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -1963,7 +1945,7 @@
         <v>3</v>
       </c>
       <c r="P25" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -1977,10 +1959,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E26">
         <v>2</v>
@@ -1998,7 +1980,7 @@
         <v>2</v>
       </c>
       <c r="P26" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -2012,10 +1994,10 @@
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E27">
         <v>2</v>
@@ -2033,45 +2015,10 @@
         <v>3</v>
       </c>
       <c r="P27" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="Q27">
         <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <v>999</v>
-      </c>
-      <c r="B28" s="1">
-        <v>1</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2083,62 +2030,125 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA8897E7-22DE-1040-965A-72767399FC92}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" t="s">
         <v>33</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>34</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>103</v>
+      </c>
+      <c r="D2">
+        <v>104</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>108</v>
+      </c>
+      <c r="D3">
+        <v>109</v>
+      </c>
+      <c r="E3">
+        <v>110</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>112</v>
+      </c>
+      <c r="D4">
+        <v>113</v>
+      </c>
+      <c r="E4">
+        <v>114</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
         <v>35</v>
       </c>
-      <c r="F1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>117</v>
+      </c>
+      <c r="D5">
+        <v>118</v>
+      </c>
+      <c r="E5">
+        <v>119</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2165,36 +2175,36 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="I1" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B2" t="b">
         <v>0</v>
@@ -2212,7 +2222,7 @@
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
@@ -2220,13 +2230,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -2241,7 +2251,7 @@
         <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -2249,7 +2259,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" t="b">
         <v>0</v>
@@ -2267,7 +2277,7 @@
         <v>4</v>
       </c>
       <c r="H4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -2275,13 +2285,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -2296,7 +2306,7 @@
         <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -2307,13 +2317,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B6" t="b">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -2328,7 +2338,7 @@
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -2339,13 +2349,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -2360,7 +2370,7 @@
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -2371,13 +2381,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B8" t="b">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D8">
         <v>12</v>
@@ -2392,7 +2402,7 @@
         <v>4</v>
       </c>
       <c r="H8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -2417,31 +2427,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="H1" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -2636,21 +2646,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" t="s">
         <v>65</v>
-      </c>
-      <c r="B1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -2659,12 +2669,12 @@
         <v>300</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B3">
         <v>30</v>
@@ -2673,7 +2683,7 @@
         <v>300</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
